--- a/Test Cases & Bug Report - API Testing Automation.xlsx
+++ b/Test Cases & Bug Report - API Testing Automation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JOJO\Projects\API Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JOJO\Projects\API Testing Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD04273-86BF-4B14-8174-F41673AE9821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303412B4-6C10-450A-BB67-7A8A79985A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BA86424B-4946-4F05-887B-AEF39B3324F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{BA86424B-4946-4F05-887B-AEF39B3324F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Case" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -583,15 +583,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -963,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37444FDC-D21E-438E-B2C7-DEE3EAF02C32}">
   <dimension ref="B2:N18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
     <col min="2" max="2" width="17.109375" style="3" customWidth="1"/>
@@ -982,17 +979,17 @@
     <col min="15" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="64.8" customHeight="1">
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="2:14" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="4" spans="2:14">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1033,7 +1030,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="57.6">
+    <row r="5" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
@@ -1074,7 +1071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="57.6">
+    <row r="6" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
@@ -1115,7 +1112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="57.6">
+    <row r="7" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
@@ -1156,7 +1153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="100.8">
+    <row r="8" spans="2:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
@@ -1197,7 +1194,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="72">
+    <row r="9" spans="2:14" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
@@ -1238,7 +1235,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="72">
+    <row r="10" spans="2:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>51</v>
       </c>
@@ -1279,7 +1276,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="72">
+    <row r="11" spans="2:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>59</v>
       </c>
@@ -1320,7 +1317,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="57.6">
+    <row r="12" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>71</v>
       </c>
@@ -1361,7 +1358,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="72">
+    <row r="13" spans="2:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
@@ -1402,7 +1399,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="72">
+    <row r="14" spans="2:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="100.8">
+    <row r="15" spans="2:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>83</v>
       </c>
@@ -1484,7 +1481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="86.4">
+    <row r="16" spans="2:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>91</v>
       </c>
@@ -1525,7 +1522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="72">
+    <row r="17" spans="2:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>96</v>
       </c>
@@ -1566,7 +1563,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="72">
+    <row r="18" spans="2:14" ht="72" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>105</v>
       </c>
@@ -1619,7 +1616,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148EB41C-FBB0-418D-BD9C-508723FD005B}">
   <dimension ref="B2:O5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
     <col min="2" max="2" width="18.6640625" style="3" customWidth="1"/>
@@ -1639,46 +1636,46 @@
     <col min="16" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="28.8">
+    <row r="2" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B2" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="28.8">
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="N4" s="7" t="s">
@@ -1688,7 +1685,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="127.8" customHeight="1">
+    <row r="5" spans="2:15" ht="127.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>119</v>
       </c>
@@ -1725,7 +1722,7 @@
       <c r="M5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="4" t="s">
         <v>123</v>
       </c>
       <c r="O5" s="4"/>
